--- a/examples/smallTest.xlsx
+++ b/examples/smallTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\o.lyttleton\Development\colectica-api\issue-65\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48411EF3-C49B-4BB0-97F4-E5F83A1BB9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1740B1C7-4497-4E1C-A03E-21BC42D4C850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="148">
   <si>
     <t>Container</t>
   </si>
@@ -40,27 +41,93 @@
     <t>NewTopic</t>
   </si>
   <si>
+    <t>Nat/step/adopt mother: PIDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> no_topic</t>
+  </si>
+  <si>
+    <t>Grandmother: PIDP</t>
+  </si>
+  <si>
+    <t>Home improvements or repairs</t>
+  </si>
+  <si>
+    <t>Last job: Registrar General's Social Class</t>
+  </si>
+  <si>
+    <t>Last job: NS-SEC</t>
+  </si>
+  <si>
+    <t>Current job: Registrar General's Social Class</t>
+  </si>
+  <si>
+    <t>Current job: NS-SEC (detailed)</t>
+  </si>
+  <si>
+    <t>Still in full-time education / never had a job</t>
+  </si>
+  <si>
     <t>sequence number of newborn child</t>
   </si>
   <si>
+    <t>Child still lives with parent</t>
+  </si>
+  <si>
+    <t>Last job: Socio-economic Group</t>
+  </si>
+  <si>
+    <t>Current job: Socio-economic Group</t>
+  </si>
+  <si>
     <t>biological father of a new entrant baby</t>
   </si>
   <si>
     <t>confirmed enumeration as twin, triplet, etc. in hh</t>
   </si>
   <si>
+    <t>Area related reasons</t>
+  </si>
+  <si>
+    <t>Housing related reasons</t>
+  </si>
+  <si>
+    <t>moved for other reasons</t>
+  </si>
+  <si>
+    <t>moved for employment reasons</t>
+  </si>
+  <si>
+    <t>pno of child</t>
+  </si>
+  <si>
+    <t>ever had step/adopted child(ren)</t>
+  </si>
+  <si>
+    <t>same employer check</t>
+  </si>
+  <si>
+    <t>moved for housing reasons</t>
+  </si>
+  <si>
     <t>us5_e_child</t>
   </si>
   <si>
     <t>us5_e_indresp</t>
   </si>
   <si>
+    <t>us5_e_youth</t>
+  </si>
+  <si>
     <t>us5_e_indall</t>
   </si>
   <si>
     <t>us5_e_newborn</t>
   </si>
   <si>
+    <t>us5_e_hhresp</t>
+  </si>
+  <si>
     <t>e_newentrant</t>
   </si>
   <si>
@@ -104,6 +171,300 @@
   </si>
   <si>
     <t>marital status changed within cohab</t>
+  </si>
+  <si>
+    <t>e_mstatch2</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/4704b935-82d7-452c-96e0-f2105914c0f5/1</t>
+  </si>
+  <si>
+    <t>marst change 2: legal marital status change</t>
+  </si>
+  <si>
+    <t>e_mstatch1</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/5ee48d6d-8ec2-4207-8263-57346b6debde/1</t>
+  </si>
+  <si>
+    <t>marst change 1: legal marital status change</t>
+  </si>
+  <si>
+    <t>e_movy15</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/98c88a2d-d39f-4f66-b698-1e3df6036970/1</t>
+  </si>
+  <si>
+    <t>e_movy14</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/de127ba7-4aa4-40b1-9162-60fbbb45d7a4/1</t>
+  </si>
+  <si>
+    <t>e_moveoth_code</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/7470c5e8-5c3a-425e-86de-f89ec2266652/1</t>
+  </si>
+  <si>
+    <t>e_movdir</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/9640621e-93de-4786-96d7-1808be0a0990/1</t>
+  </si>
+  <si>
+    <t>direct or multiple moves</t>
+  </si>
+  <si>
+    <t>e_mnspid</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/491d5fbb-ffdc-44b1-ae36-b11f5016f5b9/1</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/052b210b-cc2f-4ec9-a85c-a0dca716070b/1</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/ee80c4fa-68d3-4c1b-abe0-a027642f9672/1</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/5dcbf448-fbcf-4d3d-8197-805ebff61b35/1</t>
+  </si>
+  <si>
+    <t>e_mgxty2</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/552c4668-e967-4126-aa2d-b9fdebe67c73/1</t>
+  </si>
+  <si>
+    <t>e_mgextra</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/71713292-7846-480b-bdeb-de51383fe215/1</t>
+  </si>
+  <si>
+    <t>taken out additional mortgage</t>
+  </si>
+  <si>
+    <t>e_memploy</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/df79cb96-cb9d-452b-89b8-c1e9b64f136f/1</t>
+  </si>
+  <si>
+    <t>e_lnadopt</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/4a716cee-52fd-4b4e-9083-0c505162b5ce/1</t>
+  </si>
+  <si>
+    <t>number of step/adopted child(ren)</t>
+  </si>
+  <si>
+    <t>e_lmspy44</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/01d8a94c-a0e5-4b7a-bdac-23ae9d8a63bd/1</t>
+  </si>
+  <si>
+    <t>cohab no. 4: year ended cohab</t>
+  </si>
+  <si>
+    <t>e_lmspm4</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/da685464-6c79-460e-8428-8cbade0f9ac2/1</t>
+  </si>
+  <si>
+    <t>cohab no. 4: month ended cohab</t>
+  </si>
+  <si>
+    <t>e_lmcby44</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/ed617c90-0f25-4329-bed9-c1628f813521/1</t>
+  </si>
+  <si>
+    <t>cohab no. 4: year began cohab</t>
+  </si>
+  <si>
+    <t>e_lmcbm4</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/2e005f49-66c2-4728-8341-89a2b5ddb31f/1</t>
+  </si>
+  <si>
+    <t>cohab no. 4: month began cohab</t>
+  </si>
+  <si>
+    <t>e_livpar</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/77fbcba9-19cf-4211-9fb9-55374ff83e96/1</t>
+  </si>
+  <si>
+    <t>respondent is living at home with parent/s</t>
+  </si>
+  <si>
+    <t>e_lchno</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/49572e08-a9fe-40b0-b2bc-10d152c47f96/1</t>
+  </si>
+  <si>
+    <t>e_lchlv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/654b077c-8747-4d74-a7ed-5332e30068b2/1</t>
+  </si>
+  <si>
+    <t>e_lchal</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/7aa758a0-7d72-4ce6-9176-4d57e6073e78/1</t>
+  </si>
+  <si>
+    <t>age last lived with parent</t>
+  </si>
+  <si>
+    <t>e_ladopt</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/b971410f-5b4f-478e-aab3-aa2be7e447a2/1</t>
+  </si>
+  <si>
+    <t>e_jlseg_dv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/54a0cc05-ddc0-47f8-bcf2-4212df524a9a/1</t>
+  </si>
+  <si>
+    <t>e_jlrgsc_dv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/67f5e6e6-46c2-4be0-ba81-ae404f4d8d40/1</t>
+  </si>
+  <si>
+    <t>e_jlnssec_dv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/5d872bd1-9531-4767-b186-fe098e9cc7d4/1</t>
+  </si>
+  <si>
+    <t>e_jbseg_dv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/f5260d5e-16ff-49b2-a8ab-7fcd3eef7778/1</t>
+  </si>
+  <si>
+    <t>e_jbsat</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/c6e9985b-04ac-4f02-b7e2-a88ebf9bd44c/1</t>
+  </si>
+  <si>
+    <t>satisfaction with present job</t>
+  </si>
+  <si>
+    <t>e_jbsamr</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/f643a720-a654-45b3-a486-11eb7eac4c9d/1</t>
+  </si>
+  <si>
+    <t>e_jbrgsc_dv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/90f06f4b-3021-46de-9277-a1b45b9c2cd5/1</t>
+  </si>
+  <si>
+    <t>e_jbnssec_dv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/c39d182e-50ef-4d8b-be73-bed9938d7ab1/1</t>
+  </si>
+  <si>
+    <t>e_j1none</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/6b73b437-a259-48a7-a188-2dba3c72bace/1</t>
+  </si>
+  <si>
+    <t>e_j1mngr</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/c3db2f31-4df6-46f6-b220-ff75c0004e97/1</t>
+  </si>
+  <si>
+    <t>supervisor in first job</t>
+  </si>
+  <si>
+    <t>e_j1boss</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/e764720f-9e2e-48af-922b-c4c78cb46624/1</t>
+  </si>
+  <si>
+    <t>had employees in first job</t>
+  </si>
+  <si>
+    <t>e_intdaty_if</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/9b280bf3-54b0-41f1-8f92-57cc860454aa/1</t>
+  </si>
+  <si>
+    <t>Interview date: Year, imputation flag</t>
+  </si>
+  <si>
+    <t>e_intdatm_if</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/71f7f6f5-9759-4ebd-8890-3c336bdd06f7/1</t>
+  </si>
+  <si>
+    <t>Interview date: Month, imputation flag</t>
+  </si>
+  <si>
+    <t>e_intdatd_if</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/da91b33e-bca2-4e74-9a8b-78279b7117bc/1</t>
+  </si>
+  <si>
+    <t>Interview date: Day, imputation flag</t>
+  </si>
+  <si>
+    <t>e_housing</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/817b9cfa-c980-4627-a5a9-10da0a2df376/1</t>
+  </si>
+  <si>
+    <t>e_hhresp_dv</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/074bd61c-731c-48b0-bc5b-d39f0a4e2a60/1</t>
+  </si>
+  <si>
+    <t>Household response status</t>
+  </si>
+  <si>
+    <t>e_grmpid</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/f1a16faa-9bb9-425b-9d0a-e1d70c8decee/1</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/c4f287ee-17c0-4ed6-82a5-a5402f5dd904/1</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/6c26d4e4-4808-416a-8d9a-a2e1a135c55d/1</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/item/uk.iser.ukhls/d91aa7ae-3f7b-4807-b639-37bfbd3de132/1</t>
   </si>
 </sst>
 </file>
@@ -477,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -506,122 +867,982 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>10702</v>
+        <v>115</v>
       </c>
       <c r="F2">
-        <v>115</v>
+        <v>10702</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>10702</v>
+        <v>107</v>
       </c>
       <c r="F3">
-        <v>107</v>
+        <v>10702</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>10702</v>
+        <v>115</v>
       </c>
       <c r="F4">
-        <v>115</v>
+        <v>10702</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5">
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5">
         <v>115</v>
-      </c>
-      <c r="F5">
-        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E6">
+        <v>107</v>
+      </c>
+      <c r="F6">
         <v>10703</v>
-      </c>
-      <c r="F6">
-        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>107</v>
+      </c>
+      <c r="F7">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8">
+        <v>10201</v>
+      </c>
+      <c r="F8">
+        <v>10703</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9">
+        <v>10201</v>
+      </c>
+      <c r="F9">
+        <v>10703</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>10201</v>
+      </c>
+      <c r="F10">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>10201</v>
+      </c>
+      <c r="F11">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>102</v>
+      </c>
+      <c r="F12">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13">
+        <v>102</v>
+      </c>
+      <c r="F13">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>115</v>
+      </c>
+      <c r="F14">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>115</v>
+      </c>
+      <c r="F15">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>115</v>
+      </c>
+      <c r="F16">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>115</v>
+      </c>
+      <c r="F17">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>10904</v>
+      </c>
+      <c r="F18">
+        <v>10201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19">
+        <v>109</v>
+      </c>
+      <c r="F19">
+        <v>10904</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>102</v>
+      </c>
+      <c r="F20">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21">
+        <v>10704</v>
+      </c>
+      <c r="F21">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22">
+        <v>10703</v>
+      </c>
+      <c r="F22">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23">
+        <v>10703</v>
+      </c>
+      <c r="F23">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24">
+        <v>10703</v>
+      </c>
+      <c r="F24">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25">
+        <v>10703</v>
+      </c>
+      <c r="F25">
+        <v>10704</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26">
+        <v>10701</v>
+      </c>
+      <c r="F26">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27">
+        <v>115</v>
+      </c>
+      <c r="F27">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28">
+        <v>107</v>
+      </c>
+      <c r="F28">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29">
+        <v>111</v>
+      </c>
+      <c r="F29">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30">
+        <v>10704</v>
+      </c>
+      <c r="F30">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31">
+        <v>10901</v>
+      </c>
+      <c r="F31">
+        <v>10902</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E32">
+        <v>10901</v>
+      </c>
+      <c r="F32">
+        <v>10902</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33">
+        <v>10901</v>
+      </c>
+      <c r="F33">
+        <v>10902</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34">
+        <v>10901</v>
+      </c>
+      <c r="F34">
+        <v>10902</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" t="s">
+        <v>113</v>
+      </c>
+      <c r="D35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35">
+        <v>109</v>
+      </c>
+      <c r="F35">
+        <v>10901</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
         <v>27</v>
       </c>
-      <c r="E7">
-        <v>10702</v>
-      </c>
-      <c r="F7">
-        <v>107</v>
+      <c r="E36">
+        <v>109</v>
+      </c>
+      <c r="F36">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>10901</v>
+      </c>
+      <c r="F37">
+        <v>10902</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38">
+        <v>10901</v>
+      </c>
+      <c r="F38">
+        <v>10902</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39">
+        <v>108</v>
+      </c>
+      <c r="F39">
+        <v>10901</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40">
+        <v>109</v>
+      </c>
+      <c r="F40">
+        <v>10901</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41">
+        <v>109</v>
+      </c>
+      <c r="F41">
+        <v>10901</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45">
+        <v>102</v>
+      </c>
+      <c r="F45">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" t="s">
+        <v>141</v>
+      </c>
+      <c r="D46" t="s">
+        <v>142</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47">
+        <v>115</v>
+      </c>
+      <c r="F47">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48">
+        <v>115</v>
+      </c>
+      <c r="F48">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49">
+        <v>115</v>
+      </c>
+      <c r="F49">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50">
+        <v>115</v>
+      </c>
+      <c r="F50">
+        <v>10702</v>
       </c>
     </row>
   </sheetData>
